--- a/data/trans_orig/P33A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239928</t>
+          <t>239667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>263787</t>
+          <t>263186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>186149</t>
+          <t>185683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217652</t>
+          <t>217023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>431607</t>
+          <t>434541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>473947</t>
+          <t>475154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53858</t>
+          <t>54119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63674</t>
+          <t>64303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95177</t>
+          <t>95643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101165</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143505</t>
+          <t>140571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>397839</t>
+          <t>398476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>431754</t>
+          <t>433496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336562</t>
+          <t>338084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>382115</t>
+          <t>382273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>744309</t>
+          <t>748112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>801800</t>
+          <t>806164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66433</t>
+          <t>64691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100348</t>
+          <t>99711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138394</t>
+          <t>138236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183947</t>
+          <t>182425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216896</t>
+          <t>212532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274387</t>
+          <t>270584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>261714</t>
+          <t>261350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>285952</t>
+          <t>286679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239002</t>
+          <t>238892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272260</t>
+          <t>271799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>508871</t>
+          <t>510352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>551645</t>
+          <t>551643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>34361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59326</t>
+          <t>59690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68760</t>
+          <t>69221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102018</t>
+          <t>102128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>110417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153189</t>
+          <t>151708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273897</t>
+          <t>276033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306410</t>
+          <t>308087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210337</t>
+          <t>209577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249466</t>
+          <t>248566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495485</t>
+          <t>494058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>549152</t>
+          <t>545636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67572</t>
+          <t>65895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100085</t>
+          <t>97949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138550</t>
+          <t>139450</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177679</t>
+          <t>178439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212846</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266513</t>
+          <t>267940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176161</t>
+          <t>176244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194822</t>
+          <t>195562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139460</t>
+          <t>138458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165533</t>
+          <t>166299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>321678</t>
+          <t>322564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>357477</t>
+          <t>356454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>35332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54058</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80131</t>
+          <t>81133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>74713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109489</t>
+          <t>108603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216236</t>
+          <t>216875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241718</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191632</t>
+          <t>191115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>221764</t>
+          <t>221408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>417143</t>
+          <t>416561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457097</t>
+          <t>457102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57745</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57291</t>
+          <t>57647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>95934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135893</t>
+          <t>136475</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>543464</t>
+          <t>543888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>579453</t>
+          <t>579320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>491604</t>
+          <t>490240</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>540214</t>
+          <t>537872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1046983</t>
+          <t>1047330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1107589</t>
+          <t>1107299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>80558</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116414</t>
+          <t>115990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>151390</t>
+          <t>153732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>201364</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>243893</t>
+          <t>244183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>304499</t>
+          <t>304152</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>650687</t>
+          <t>650679</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>689745</t>
+          <t>688257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>642659</t>
+          <t>642843</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>687956</t>
+          <t>687729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1306972</t>
+          <t>1303190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1363832</t>
+          <t>1365054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79463</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118521</t>
+          <t>118529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>122697</t>
+          <t>122924</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167994</t>
+          <t>167810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>216029</t>
+          <t>214807</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>272889</t>
+          <t>276671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2846952</t>
+          <t>2845639</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2930374</t>
+          <t>2929184</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2533864</t>
+          <t>2541286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2643192</t>
+          <t>2650275</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5407116</t>
+          <t>5409254</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5548949</t>
+          <t>5550043</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>471264</t>
+          <t>472454</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>554686</t>
+          <t>555999</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>888582</t>
+          <t>881499</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>997910</t>
+          <t>990488</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1384463</t>
+          <t>1383369</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1526296</t>
+          <t>1524158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207610</t>
+          <t>208362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239538</t>
+          <t>238543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163428</t>
+          <t>161575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>197119</t>
+          <t>195549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382377</t>
+          <t>382576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427342</t>
+          <t>426354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>52219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>82400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87012</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120703</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147551</t>
+          <t>148539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192516</t>
+          <t>192317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>450802</t>
+          <t>451382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>473729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>404601</t>
+          <t>408213</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>441513</t>
+          <t>441590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>866913</t>
+          <t>866445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>911639</t>
+          <t>908800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50754</t>
+          <t>50174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76818</t>
+          <t>76741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113730</t>
+          <t>110118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108248</t>
+          <t>111087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152974</t>
+          <t>153442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>273925</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294300</t>
+          <t>294793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>242902</t>
+          <t>241079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271848</t>
+          <t>272251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526149</t>
+          <t>526490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>559928</t>
+          <t>561026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>38960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83542</t>
+          <t>85365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80004</t>
+          <t>78906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>113442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>277061</t>
+          <t>278507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310038</t>
+          <t>310160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224684</t>
+          <t>224884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264407</t>
+          <t>263712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511881</t>
+          <t>511117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563015</t>
+          <t>563182</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>58991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92090</t>
+          <t>90644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116566</t>
+          <t>117261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156289</t>
+          <t>156089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187109</t>
+          <t>186942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238243</t>
+          <t>239007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148972</t>
+          <t>148385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173357</t>
+          <t>173576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155539</t>
+          <t>154579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179243</t>
+          <t>178681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314017</t>
+          <t>313236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346005</t>
+          <t>346545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>36685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61289</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81862</t>
+          <t>81322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113850</t>
+          <t>114631</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>206123</t>
+          <t>204899</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>228487</t>
+          <t>228097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>176547</t>
+          <t>176427</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>206262</t>
+          <t>207629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>392530</t>
+          <t>392374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428994</t>
+          <t>429035</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56674</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86389</t>
+          <t>86509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90878</t>
+          <t>90837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127342</t>
+          <t>127498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>513559</t>
+          <t>515521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555765</t>
+          <t>557077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>474543</t>
+          <t>478006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>523313</t>
+          <t>526107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1006745</t>
+          <t>1004739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1070999</t>
+          <t>1069087</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93719</t>
+          <t>92407</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135925</t>
+          <t>133963</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162830</t>
+          <t>160036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211600</t>
+          <t>208137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264628</t>
+          <t>266540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>328882</t>
+          <t>330888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>620404</t>
+          <t>621473</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>661394</t>
+          <t>661768</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>578427</t>
+          <t>578550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>629393</t>
+          <t>630167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1209665</t>
+          <t>1212537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1279864</t>
+          <t>1281115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104732</t>
+          <t>104358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145722</t>
+          <t>144653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191998</t>
+          <t>191224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>242964</t>
+          <t>242841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307654</t>
+          <t>306403</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>377853</t>
+          <t>374981</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2780307</t>
+          <t>2781398</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2867078</t>
+          <t>2867936</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2518655</t>
+          <t>2525687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2629061</t>
+          <t>2631907</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5332697</t>
+          <t>5337494</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5473929</t>
+          <t>5476983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>490686</t>
+          <t>489828</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>577457</t>
+          <t>576366</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>868894</t>
+          <t>866048</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>979300</t>
+          <t>972268</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1381790</t>
+          <t>1378736</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1523022</t>
+          <t>1518225</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>278271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296916</t>
+          <t>297067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242425</t>
+          <t>242326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259757</t>
+          <t>259902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>527876</t>
+          <t>527786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>552398</t>
+          <t>553170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47210</t>
+          <t>47309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48679</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73201</t>
+          <t>73291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>401770</t>
+          <t>398608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>444269</t>
+          <t>443133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>355573</t>
+          <t>354064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>390179</t>
+          <t>389952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>767797</t>
+          <t>770940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>825372</t>
+          <t>827293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71905</t>
+          <t>73041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114404</t>
+          <t>117566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121369</t>
+          <t>121596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155975</t>
+          <t>157484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>202350</t>
+          <t>200429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259925</t>
+          <t>256782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>245316</t>
+          <t>247003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272010</t>
+          <t>273067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>268405</t>
+          <t>268435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293016</t>
+          <t>292486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>523741</t>
+          <t>521471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>559056</t>
+          <t>559029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68749</t>
+          <t>67062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54762</t>
+          <t>55292</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79373</t>
+          <t>79343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102787</t>
+          <t>102814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138102</t>
+          <t>140372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>226362</t>
+          <t>229412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>260748</t>
+          <t>261153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>331614</t>
+          <t>328185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>402983</t>
+          <t>403805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>575760</t>
+          <t>576274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652898</t>
+          <t>653176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50459</t>
+          <t>50054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84845</t>
+          <t>81795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69893</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141262</t>
+          <t>144691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131186</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208324</t>
+          <t>207810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157696</t>
+          <t>156672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168221</t>
+          <t>168311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172674</t>
+          <t>173228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186545</t>
+          <t>186232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>334231</t>
+          <t>333837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352010</t>
+          <t>352124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205040</t>
+          <t>205555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>227795</t>
+          <t>228781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>173513</t>
+          <t>173126</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>195867</t>
+          <t>195275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>385362</t>
+          <t>387947</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>418544</t>
+          <t>419328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41841</t>
+          <t>40855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64596</t>
+          <t>64081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61189</t>
+          <t>61781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83543</t>
+          <t>83930</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108148</t>
+          <t>107364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141330</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>467349</t>
+          <t>469728</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>515165</t>
+          <t>517352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>588428</t>
+          <t>590886</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>745302</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1092114</t>
+          <t>1092696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1261222</t>
+          <t>1253053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98901</t>
+          <t>96714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146717</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87227</t>
+          <t>80011</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244101</t>
+          <t>241643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185373</t>
+          <t>193542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354481</t>
+          <t>353899</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>723017</t>
+          <t>720948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>866483</t>
+          <t>859739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>464080</t>
+          <t>463521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>504993</t>
+          <t>504165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1190389</t>
+          <t>1191882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1413778</t>
+          <t>1418767</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62237</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>205703</t>
+          <t>207772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>210399</t>
+          <t>211227</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>251312</t>
+          <t>251871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230334</t>
+          <t>225345</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>453723</t>
+          <t>452230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2815441</t>
+          <t>2817174</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3019981</t>
+          <t>3008245</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2701516</t>
+          <t>2698962</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2958545</t>
+          <t>2930686</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5531279</t>
+          <t>5548185</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5816066</t>
+          <t>5831254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>423458</t>
+          <t>435194</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>627998</t>
+          <t>626265</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>675481</t>
+          <t>703340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>932510</t>
+          <t>935064</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1261399</t>
+          <t>1246211</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1546186</t>
+          <t>1529280</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239667</t>
+          <t>240250</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>263186</t>
+          <t>263886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185683</t>
+          <t>186855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217023</t>
+          <t>217472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>434541</t>
+          <t>433941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>475154</t>
+          <t>475428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54119</t>
+          <t>53536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95643</t>
+          <t>94471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>99684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140571</t>
+          <t>141171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398476</t>
+          <t>397931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>433496</t>
+          <t>432930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338084</t>
+          <t>336029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>382273</t>
+          <t>380994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>748112</t>
+          <t>747345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>806164</t>
+          <t>805113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>65257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99711</t>
+          <t>100256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138236</t>
+          <t>139515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182425</t>
+          <t>184480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212532</t>
+          <t>213583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270584</t>
+          <t>271351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>261350</t>
+          <t>261149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>286679</t>
+          <t>286170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>238892</t>
+          <t>239407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271799</t>
+          <t>271540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>510352</t>
+          <t>509211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>551643</t>
+          <t>549939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34361</t>
+          <t>34870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>59891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69221</t>
+          <t>69480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102128</t>
+          <t>101613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110417</t>
+          <t>112121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151708</t>
+          <t>152849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276033</t>
+          <t>274975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>308087</t>
+          <t>308027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>209577</t>
+          <t>208284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>248566</t>
+          <t>247879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>494058</t>
+          <t>495328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>545636</t>
+          <t>547758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65895</t>
+          <t>65955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97949</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139450</t>
+          <t>140137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178439</t>
+          <t>179732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>214240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267940</t>
+          <t>266670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176244</t>
+          <t>176832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195562</t>
+          <t>196293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138458</t>
+          <t>138136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166299</t>
+          <t>166033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322564</t>
+          <t>323278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356454</t>
+          <t>356857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35332</t>
+          <t>34744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>53558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81133</t>
+          <t>81455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74713</t>
+          <t>74310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108603</t>
+          <t>107889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216875</t>
+          <t>215345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191115</t>
+          <t>191310</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>221408</t>
+          <t>222072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>416561</t>
+          <t>415919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457102</t>
+          <t>457021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>58636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>56983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>87745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95934</t>
+          <t>96015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136475</t>
+          <t>137117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>543888</t>
+          <t>542813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>579320</t>
+          <t>578359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>490240</t>
+          <t>491985</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>537872</t>
+          <t>540624</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1047330</t>
+          <t>1047035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1107299</t>
+          <t>1107667</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80558</t>
+          <t>81519</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115990</t>
+          <t>117065</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>153732</t>
+          <t>150980</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201364</t>
+          <t>199619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244183</t>
+          <t>243815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>304152</t>
+          <t>304447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>650679</t>
+          <t>648861</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>688257</t>
+          <t>687043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>642843</t>
+          <t>641109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>687729</t>
+          <t>686017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1303190</t>
+          <t>1304920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1365054</t>
+          <t>1366022</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80951</t>
+          <t>82165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118529</t>
+          <t>120347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>122924</t>
+          <t>124636</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167810</t>
+          <t>169544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>214807</t>
+          <t>213839</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>276671</t>
+          <t>274941</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2845639</t>
+          <t>2839887</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2929184</t>
+          <t>2926110</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2541286</t>
+          <t>2535855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2650275</t>
+          <t>2647044</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5409254</t>
+          <t>5410910</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5550043</t>
+          <t>5545467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>472454</t>
+          <t>475528</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>555999</t>
+          <t>561751</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>881499</t>
+          <t>884730</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>990488</t>
+          <t>995919</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1383369</t>
+          <t>1387945</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1524158</t>
+          <t>1522502</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208362</t>
+          <t>209544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238543</t>
+          <t>238485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161575</t>
+          <t>163014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195549</t>
+          <t>196492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382576</t>
+          <t>380769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>426354</t>
+          <t>423131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82400</t>
+          <t>81218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88582</t>
+          <t>87639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122556</t>
+          <t>121117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148539</t>
+          <t>151762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192317</t>
+          <t>194124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>451382</t>
+          <t>449973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>473729</t>
+          <t>473268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>408213</t>
+          <t>407343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>441590</t>
+          <t>443076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>866445</t>
+          <t>863610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>908800</t>
+          <t>907564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>51583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76741</t>
+          <t>75255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110118</t>
+          <t>110988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111087</t>
+          <t>112323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153442</t>
+          <t>156277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>274529</t>
+          <t>274127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294793</t>
+          <t>294831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>241079</t>
+          <t>242186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272251</t>
+          <t>271866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526490</t>
+          <t>524530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>561026</t>
+          <t>559714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>39362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54193</t>
+          <t>54578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85365</t>
+          <t>84258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78906</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113442</t>
+          <t>115402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>278507</t>
+          <t>279163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310160</t>
+          <t>310092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224884</t>
+          <t>223571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263712</t>
+          <t>262862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511117</t>
+          <t>512712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563182</t>
+          <t>563308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58991</t>
+          <t>59059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90644</t>
+          <t>89988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117261</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156089</t>
+          <t>157402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186942</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239007</t>
+          <t>237412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148385</t>
+          <t>148887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173576</t>
+          <t>173771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154579</t>
+          <t>154792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178681</t>
+          <t>178582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>313236</t>
+          <t>312253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346545</t>
+          <t>347197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>61374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>62814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81322</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114631</t>
+          <t>115614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>204899</t>
+          <t>205363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>228097</t>
+          <t>228433</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>176427</t>
+          <t>176771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>207629</t>
+          <t>205581</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>392374</t>
+          <t>391756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>429035</t>
+          <t>428610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>57355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86509</t>
+          <t>86165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90837</t>
+          <t>91262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127498</t>
+          <t>128116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>515521</t>
+          <t>516522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>557077</t>
+          <t>557853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>478006</t>
+          <t>476100</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>526107</t>
+          <t>525581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1004739</t>
+          <t>1007610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1069087</t>
+          <t>1071303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92407</t>
+          <t>91631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133963</t>
+          <t>132962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>160036</t>
+          <t>160562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208137</t>
+          <t>210043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266540</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>330888</t>
+          <t>328017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>621473</t>
+          <t>622477</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>661768</t>
+          <t>661013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>578550</t>
+          <t>577798</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>630167</t>
+          <t>630892</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1212537</t>
+          <t>1214747</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1281115</t>
+          <t>1279150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104358</t>
+          <t>105113</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144653</t>
+          <t>143649</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191224</t>
+          <t>190499</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>242841</t>
+          <t>243593</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>306403</t>
+          <t>308368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374981</t>
+          <t>372771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2781398</t>
+          <t>2782116</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2867936</t>
+          <t>2866482</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2525687</t>
+          <t>2519415</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2631907</t>
+          <t>2626052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5337494</t>
+          <t>5338511</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5476983</t>
+          <t>5475874</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>489828</t>
+          <t>491282</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>576366</t>
+          <t>575648</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>866048</t>
+          <t>871903</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>972268</t>
+          <t>978540</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1378736</t>
+          <t>1379845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1518225</t>
+          <t>1517208</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>289267</t>
+          <t>295682</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278271</t>
+          <t>285496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297067</t>
+          <t>303844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>251889</t>
+          <t>275014</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242326</t>
+          <t>264281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259902</t>
+          <t>283472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>541156</t>
+          <t>570696</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>527786</t>
+          <t>558107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>553170</t>
+          <t>583313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>23163</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33172</t>
+          <t>33349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>41047</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47309</t>
+          <t>51780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>64210</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47907</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73291</t>
+          <t>76799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>424895</t>
+          <t>438390</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398608</t>
+          <t>415074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>443133</t>
+          <t>458813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>373642</t>
+          <t>394495</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>354064</t>
+          <t>376409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>389952</t>
+          <t>411044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>798537</t>
+          <t>832884</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>770940</t>
+          <t>805144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>827293</t>
+          <t>859684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91279</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>69572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117566</t>
+          <t>113311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>137906</t>
+          <t>148504</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121596</t>
+          <t>131955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157484</t>
+          <t>166590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>229185</t>
+          <t>238500</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200429</t>
+          <t>211700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256782</t>
+          <t>266240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516174</t>
+          <t>528385</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516174</t>
+          <t>528385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516174</t>
+          <t>528385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>542999</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>542999</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>542999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1027722</t>
+          <t>1071384</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1027722</t>
+          <t>1071384</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1027722</t>
+          <t>1071384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>260479</t>
+          <t>260347</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>247003</t>
+          <t>247051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>273067</t>
+          <t>272126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>281201</t>
+          <t>286738</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>268435</t>
+          <t>274783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292486</t>
+          <t>299156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>541680</t>
+          <t>547085</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>521471</t>
+          <t>529434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>559029</t>
+          <t>564977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53586</t>
+          <t>53680</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>41901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67062</t>
+          <t>66976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66577</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55292</t>
+          <t>55875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79343</t>
+          <t>80248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>120163</t>
+          <t>121973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>104081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140372</t>
+          <t>139624</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347778</t>
+          <t>355031</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347778</t>
+          <t>355031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347778</t>
+          <t>355031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>661843</t>
+          <t>669058</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661843</t>
+          <t>669058</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>661843</t>
+          <t>669058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>245907</t>
+          <t>299173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229412</t>
+          <t>278119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261153</t>
+          <t>315527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>361914</t>
+          <t>296313</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>328185</t>
+          <t>278421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>403805</t>
+          <t>312934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>607821</t>
+          <t>595486</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576274</t>
+          <t>566745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>653176</t>
+          <t>619226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>65300</t>
+          <t>72492</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>56138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81795</t>
+          <t>93546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>110962</t>
+          <t>122614</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>105993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144691</t>
+          <t>140506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>176263</t>
+          <t>195107</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130908</t>
+          <t>171367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207810</t>
+          <t>223848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311207</t>
+          <t>371665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311207</t>
+          <t>371665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311207</t>
+          <t>371665</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>472876</t>
+          <t>418927</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>472876</t>
+          <t>418927</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>472876</t>
+          <t>418927</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>784084</t>
+          <t>790593</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>784084</t>
+          <t>790593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>784084</t>
+          <t>790593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>163220</t>
+          <t>189002</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156672</t>
+          <t>181731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168311</t>
+          <t>194050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>180581</t>
+          <t>196894</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173228</t>
+          <t>188885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186232</t>
+          <t>203047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>343802</t>
+          <t>385894</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333837</t>
+          <t>375126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352124</t>
+          <t>394724</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28728</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33984</t>
+          <t>36737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>41538</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>55469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178128</t>
+          <t>204974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178128</t>
+          <t>204974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178128</t>
+          <t>204974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>225622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>225622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>225622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385340</t>
+          <t>430595</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385340</t>
+          <t>430595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385340</t>
+          <t>430595</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>217570</t>
+          <t>218797</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205555</t>
+          <t>206993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>228781</t>
+          <t>229830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>185050</t>
+          <t>189618</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>173126</t>
+          <t>178378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>195275</t>
+          <t>201021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>402620</t>
+          <t>408415</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>387947</t>
+          <t>391582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>419328</t>
+          <t>423345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52066</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40855</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64081</t>
+          <t>63714</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>72006</t>
+          <t>74132</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61781</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83930</t>
+          <t>85372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>124072</t>
+          <t>126042</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107364</t>
+          <t>111112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138745</t>
+          <t>142875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>495092</t>
+          <t>581052</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>469728</t>
+          <t>556502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>517352</t>
+          <t>602424</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>656152</t>
+          <t>538519</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>590886</t>
+          <t>515788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>563158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1151244</t>
+          <t>1119570</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1092696</t>
+          <t>1087854</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1253053</t>
+          <t>1153074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>118974</t>
+          <t>128131</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96714</t>
+          <t>106759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144338</t>
+          <t>152681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>176377</t>
+          <t>216103</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>191464</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>241643</t>
+          <t>238834</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>295351</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>193542</t>
+          <t>310730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>353899</t>
+          <t>375950</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>614066</t>
+          <t>709183</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>614066</t>
+          <t>709183</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>614066</t>
+          <t>709183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>832529</t>
+          <t>754622</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>832529</t>
+          <t>754622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>832529</t>
+          <t>754622</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1446595</t>
+          <t>1463804</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1446595</t>
+          <t>1463804</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1446595</t>
+          <t>1463804</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>782752</t>
+          <t>632849</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>720948</t>
+          <t>610782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>859739</t>
+          <t>655351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>485273</t>
+          <t>564085</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>463521</t>
+          <t>540142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>504165</t>
+          <t>589114</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1268026</t>
+          <t>1196934</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1191882</t>
+          <t>1164125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1418767</t>
+          <t>1228724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>145968</t>
+          <t>165223</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>142721</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>207772</t>
+          <t>187290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>230119</t>
+          <t>266524</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>211227</t>
+          <t>241495</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>251871</t>
+          <t>290467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>376086</t>
+          <t>431747</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>225345</t>
+          <t>399957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>452230</t>
+          <t>464556</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2879182</t>
+          <t>2915291</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2817174</t>
+          <t>2862662</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3008245</t>
+          <t>2963252</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2775703</t>
+          <t>2741673</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2698962</t>
+          <t>2694831</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2930686</t>
+          <t>2785051</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5654885</t>
+          <t>5656964</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5548185</t>
+          <t>5593634</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5831254</t>
+          <t>5724172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>564257</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>435194</t>
+          <t>552606</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>626265</t>
+          <t>653196</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>858323</t>
+          <t>965947</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>703340</t>
+          <t>922569</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>935064</t>
+          <t>1012789</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1422580</t>
+          <t>1566514</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1246211</t>
+          <t>1499306</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1529280</t>
+          <t>1629844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
